--- a/Fase 2/Evidencias Grupales/PLANILLA DE EVALUACION AVANCE FASE 2.xlsx
+++ b/Fase 2/Evidencias Grupales/PLANILLA DE EVALUACION AVANCE FASE 2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Clases\DUOC\CAPSTONE\2025-2\Rúbricas\4D\Fase 2\--Equipo 4 (Documento incompleto, Evidencias proyecto)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75BFEEE-FA98-43B9-90A2-BD0AE48F865B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68F420D-7A20-43D1-B202-A838DBC6ED23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C4" s="5">
         <f>EVALUACION2!$C$22</f>
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C5" s="5">
         <f>EVALUACION2!$C$22</f>
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -1320,7 +1320,7 @@
       <c r="B6" s="25"/>
       <c r="C6" s="5">
         <f>EVALUACION2!$C$22</f>
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -1415,23 +1415,23 @@
         <v>2. Aplica una metodología que permite el logro de los objetivos propuestos, de acuerdo a los estándares de la disciplina.</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="15" t="str">
+        <v>X</v>
+      </c>
+      <c r="E14" s="15">
         <f>IF(D14="X",100*0.1,"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="F14" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
-      </c>
-      <c r="G14" s="15">
+        <v/>
+      </c>
+      <c r="G14" s="15" t="str">
         <f>IF(F14="X",60*0.1,"")</f>
-        <v>6</v>
+        <v/>
       </c>
       <c r="H14" s="15" t="str">
         <f t="shared" si="2"/>
@@ -1499,23 +1499,23 @@
         <v>4. Utiliza de manera precisa el lenguaje técnico en los entregables de acuerdo con lo requerido por la disciplina.</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="15" t="str">
+        <v>X</v>
+      </c>
+      <c r="E16" s="15">
         <f>IF(D16="X",100*0.05,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="F16" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
-      </c>
-      <c r="G16" s="15">
+        <v/>
+      </c>
+      <c r="G16" s="15" t="str">
         <f>IF(F16="X",60*0.05,"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="H16" s="15" t="str">
         <f t="shared" si="2"/>
@@ -1583,23 +1583,23 @@
         <v>6. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estrucutra y nombres solicitados, guardando todas las evidencias de avances en Git</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15" t="str">
         <f>IF($C18=CL,"X","")</f>
-        <v/>
-      </c>
-      <c r="E18" s="15" t="str">
+        <v>X</v>
+      </c>
+      <c r="E18" s="15">
         <f>IF(D18="X",100*0.2,"")</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="F18" s="15" t="str">
         <f>IF($C18=L,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="G18" s="15">
+        <v/>
+      </c>
+      <c r="G18" s="15" t="str">
         <f>IF(F18="X",60*0.2,"")</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="H18" s="15" t="str">
         <f>IF($C18=ML,"X","")</f>
@@ -1667,23 +1667,23 @@
         <v>8. Demuestra un trabajo en equipo en donde todos los miembros del equipo expresan con fluidez el conocimiento del tema expuesto y  participan de las actividades planificadas en el proyecto</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="15" t="str">
         <f>IF($C20=CL,"X","")</f>
-        <v/>
-      </c>
-      <c r="E20" s="15" t="str">
+        <v>X</v>
+      </c>
+      <c r="E20" s="15">
         <f>IF(D20="X",100*0.1,"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="F20" s="15" t="str">
         <f>IF($C20=L,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="G20" s="15">
+        <v/>
+      </c>
+      <c r="G20" s="15" t="str">
         <f>IF(F20="X",60*0.1,"")</f>
-        <v>6</v>
+        <v/>
       </c>
       <c r="H20" s="15" t="str">
         <f>IF($C20=ML,"X","")</f>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="C21" s="31">
         <f>E21+G21+I21+K21</f>
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D21" s="16"/>
       <c r="E21" s="16">
         <f>SUM(E13:E20)</f>
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="16">
         <f>SUM(G13:G20)</f>
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="H21" s="16"/>
       <c r="I21" s="16">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C22" s="17">
         <f>VLOOKUP(C21,ESCALA_IEP!A2:B202,2,FALSE)</f>
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
